--- a/дебеторка.xlsx
+++ b/дебеторка.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\Дебетовий\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\simplepython\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F49DF8-C5AC-40E7-B66C-93A7F62FE117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7793B85-9324-4E82-BDD0-5A071AC9864E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="14386" xr2:uid="{7D05D760-E367-4CEE-BD76-DFCA9618AD5F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="187">
   <si>
     <t>рахунок</t>
   </si>
@@ -116,9 +116,6 @@
     <t>товариство</t>
   </si>
   <si>
-    <t>ЗІА</t>
-  </si>
-  <si>
     <t>Загалом</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
     <t>BA5530ЕX</t>
   </si>
   <si>
-    <t>18.062026</t>
-  </si>
-  <si>
     <t>ВА0251 НЕ</t>
   </si>
   <si>
@@ -282,9 +276,6 @@
   </si>
   <si>
     <t>готівка</t>
-  </si>
-  <si>
-    <t>АВТОСВІФТ</t>
   </si>
   <si>
     <t>Сумська обл-ть, Краснопільський р-н, с.Краспопілля-Одеський Морський Торгівельний Порт</t>
@@ -603,13 +594,13 @@
     <t>не зрозуміло з якою вагою розвантаження</t>
   </si>
   <si>
-    <t>Приватний двір</t>
-  </si>
-  <si>
     <t>Дяченко О.Ю.</t>
   </si>
   <si>
     <t>накази та цпх</t>
+  </si>
+  <si>
+    <t>ЗІАВТОТРАНС</t>
   </si>
 </sst>
 </file>
@@ -724,42 +715,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
@@ -887,6 +842,42 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -903,16 +894,16 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3E9C3FE4-C972-4EBE-A59C-DE3FAFB6B53C}" name="Table1" displayName="Table1" ref="A1:W60" totalsRowCount="1">
   <tableColumns count="23">
-    <tableColumn id="19" xr3:uid="{CE7D7A56-2867-4113-BEA2-2556E2366495}" name="накази та цпх" dataDxfId="0" totalsRowDxfId="1"/>
-    <tableColumn id="1" xr3:uid="{DFB1DB8B-6D9B-49C4-89E7-3347623EBB8F}" name="нотатка" totalsRowLabel="Загалом" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="23" xr3:uid="{8F6734DD-A9B1-40DB-BBE5-83091D398B44}" name="номернклатура (вантаж, маршрут)" dataDxfId="15">
+    <tableColumn id="19" xr3:uid="{CE7D7A56-2867-4113-BEA2-2556E2366495}" name="накази та цпх" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{DFB1DB8B-6D9B-49C4-89E7-3347623EBB8F}" name="нотатка" totalsRowLabel="Загалом" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="23" xr3:uid="{8F6734DD-A9B1-40DB-BBE5-83091D398B44}" name="номернклатура (вантаж, маршрут)" dataDxfId="13">
       <calculatedColumnFormula>IF(
     OR(ISBLANK(Table1[[#This Row],[вантаж (родовий відмінок)]]), ISBLANK(Table1[[#This Row],[маршрут згідно товаро-транспортній накладній]])),
     "",
     "Послуги перевезення " &amp; Table1[[#This Row],[вантаж (родовий відмінок)]] &amp; " за маршрутом " &amp; Table1[[#This Row],[маршрут згідно товаро-транспортній накладній]]
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{C1909F87-8435-4E72-8036-983D05FC70A2}" name="номенклатура (вантаж, маршрут, авто, причіп, водій)" dataDxfId="14">
+    <tableColumn id="22" xr3:uid="{C1909F87-8435-4E72-8036-983D05FC70A2}" name="номенклатура (вантаж, маршрут, авто, причіп, водій)" dataDxfId="12">
       <calculatedColumnFormula>IF(
     OR(
         ISBLANK(Table1[[#This Row],[вантаж (родовий відмінок)]]),
@@ -929,36 +920,36 @@
     ", водій " &amp; Table1[[#This Row],[водій]]
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{4391925A-EF84-4D35-95B4-EB15C6302FBE}" name="вага загальна до рахунку" dataDxfId="13" totalsRowDxfId="12">
+    <tableColumn id="25" xr3:uid="{4391925A-EF84-4D35-95B4-EB15C6302FBE}" name="вага загальна до рахунку" dataDxfId="11" totalsRowDxfId="10">
       <calculatedColumnFormula>IF(SUMIFS(Table1[розвантаження вага тонни], Table1[товариство], Table1[[#This Row],[товариство]], Table1[рахунок], Table1[[#This Row],[рахунок]])=0, "", SUMIFS(Table1[розвантаження вага тонни], Table1[товариство], Table1[[#This Row],[товариство]], Table1[рахунок], Table1[[#This Row],[рахунок]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{4A12C982-6778-41BD-BCDD-8CF6D1227AED}" name="ціна за тонну без ПДВ" dataDxfId="11">
+    <tableColumn id="14" xr3:uid="{4A12C982-6778-41BD-BCDD-8CF6D1227AED}" name="ціна за тонну без ПДВ" dataDxfId="9">
       <calculatedColumnFormula>IF(Table1[[#This Row],[ціна за тонну з ПДВ]]/1.2=0, "", Table1[[#This Row],[ціна за тонну з ПДВ]]/1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1EAB3D95-7280-4FB8-A4D2-6BA7B217D243}" name="рахунок" dataDxfId="10">
+    <tableColumn id="2" xr3:uid="{1EAB3D95-7280-4FB8-A4D2-6BA7B217D243}" name="рахунок" dataDxfId="8">
       <calculatedColumnFormula>""</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{79A06E1C-B3EA-4A09-825F-A65CB4DF8FC9}" name="наявність ттн офіс"/>
     <tableColumn id="27" xr3:uid="{157AF330-BCCC-4CBD-9688-5EB144BE30F0}" name="товариство"/>
     <tableColumn id="18" xr3:uid="{039A50B9-DA25-4627-8311-CEB29A4A6D2E}" name="замовник"/>
     <tableColumn id="21" xr3:uid="{F15E099A-1503-4CB8-8BA2-1A66A93D8191}" name="номер ттн"/>
-    <tableColumn id="4" xr3:uid="{AE1D7F59-ECD2-4C02-971E-173991F8B0FC}" name="навантаження дата" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{4AF1B38B-ABD9-4F93-9AF7-C05FD841B379}" name="розвантаження дата" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{AE1D7F59-ECD2-4C02-971E-173991F8B0FC}" name="навантаження дата" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{4AF1B38B-ABD9-4F93-9AF7-C05FD841B379}" name="розвантаження дата" dataDxfId="6"/>
     <tableColumn id="6" xr3:uid="{262ACE03-A001-4FEF-8352-07C5AD9453D9}" name="авто"/>
     <tableColumn id="7" xr3:uid="{E1586D8C-984E-4CAC-B8F6-B48095EB7897}" name="причіп"/>
     <tableColumn id="8" xr3:uid="{59998F9D-0367-40FF-ABA4-9328F3D57B00}" name="водій"/>
     <tableColumn id="9" xr3:uid="{28A37922-319E-44EB-8B11-BA5E6B53569A}" name="маршрут згідно товаро-транспортній накладній"/>
     <tableColumn id="10" xr3:uid="{6177818A-07CF-4602-BB28-B917DBB496BF}" name="вантаж (родовий відмінок)"/>
-    <tableColumn id="11" xr3:uid="{2DDFF24E-F72C-4E87-A94B-E7071A9EC8DA}" name="навантаження вага тонни" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{D49649F1-7EC7-497D-A60D-C9C7B410835E}" name="розвантаження вага тонни" totalsRowFunction="custom" dataDxfId="6">
+    <tableColumn id="11" xr3:uid="{2DDFF24E-F72C-4E87-A94B-E7071A9EC8DA}" name="навантаження вага тонни" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{D49649F1-7EC7-497D-A60D-C9C7B410835E}" name="розвантаження вага тонни" totalsRowFunction="custom" dataDxfId="4">
       <totalsRowFormula>SUBTOTAL(109, Table1[розвантаження вага тонни])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{9F79077D-C08D-4306-994F-0B3B916219E7}" name="ціна за тонну з ПДВ" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{7B72B004-D4A0-4B4A-B93D-7FF0CA973B12}" name="сума з ПДВ" totalsRowFunction="custom" dataDxfId="4">
+    <tableColumn id="13" xr3:uid="{9F79077D-C08D-4306-994F-0B3B916219E7}" name="ціна за тонну з ПДВ" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{7B72B004-D4A0-4B4A-B93D-7FF0CA973B12}" name="сума з ПДВ" totalsRowFunction="custom" dataDxfId="2">
       <calculatedColumnFormula>IF(Table1[[#This Row],[розвантаження вага тонни]]*Table1[[#This Row],[ціна за тонну з ПДВ]]=0, "", Table1[[#This Row],[розвантаження вага тонни]]*Table1[[#This Row],[ціна за тонну з ПДВ]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109, Table1[сума з ПДВ])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{69BDB6D5-3A26-4503-A19D-87584DD2493E}" name="сума без ПДВ" totalsRowFunction="sum" dataDxfId="3" totalsRowDxfId="2">
+    <tableColumn id="16" xr3:uid="{69BDB6D5-3A26-4503-A19D-87584DD2493E}" name="сума без ПДВ" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>IFERROR(IF(Table1[[#This Row],[сума з ПДВ]]/1.2=0, "", Table1[[#This Row],[сума з ПДВ]]/1.2), "")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1311,7 +1302,7 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
@@ -1338,7 +1329,7 @@
         <v>24</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>12</v>
@@ -1365,10 +1356,10 @@
         <v>23</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U1" s="6" t="s">
         <v>7</v>
@@ -1423,7 +1414,7 @@
         <v>4</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="K2">
         <v>6</v>
@@ -1511,10 +1502,10 @@
         <v>4</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K3">
         <v>199761</v>
@@ -1526,19 +1517,19 @@
         <v>46192</v>
       </c>
       <c r="N3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P3" t="s">
         <v>48</v>
       </c>
-      <c r="P3" t="s">
-        <v>49</v>
-      </c>
       <c r="Q3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S3" s="4">
         <v>27.08</v>
@@ -1602,10 +1593,10 @@
         <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K4">
         <v>199762</v>
@@ -1617,19 +1608,19 @@
         <v>46191</v>
       </c>
       <c r="N4" t="s">
+        <v>34</v>
+      </c>
+      <c r="O4" t="s">
         <v>35</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>36</v>
       </c>
-      <c r="P4" t="s">
-        <v>37</v>
-      </c>
       <c r="Q4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S4" s="4">
         <v>25.42</v>
@@ -1693,10 +1684,10 @@
         <v>2</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K5">
         <v>13</v>
@@ -1708,16 +1699,16 @@
         <v>46193</v>
       </c>
       <c r="N5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O5" t="s">
+        <v>118</v>
+      </c>
+      <c r="P5" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q5" t="s">
         <v>121</v>
-      </c>
-      <c r="P5" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>124</v>
       </c>
       <c r="R5" t="s">
         <v>20</v>
@@ -1784,10 +1775,10 @@
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K6">
         <v>4</v>
@@ -1799,16 +1790,16 @@
         <v>46191</v>
       </c>
       <c r="N6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P6" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q6" t="s">
         <v>121</v>
-      </c>
-      <c r="P6" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>124</v>
       </c>
       <c r="R6" t="s">
         <v>20</v>
@@ -1875,10 +1866,10 @@
         <v>2</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1890,16 +1881,16 @@
         <v>46190</v>
       </c>
       <c r="N7" t="s">
+        <v>40</v>
+      </c>
+      <c r="O7" t="s">
         <v>41</v>
       </c>
-      <c r="O7" t="s">
-        <v>42</v>
-      </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="R7" t="s">
         <v>20</v>
@@ -1966,10 +1957,10 @@
         <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K8">
         <v>37</v>
@@ -1981,16 +1972,16 @@
         <v>46189</v>
       </c>
       <c r="N8" t="s">
+        <v>42</v>
+      </c>
+      <c r="O8" t="s">
         <v>43</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>44</v>
       </c>
-      <c r="P8" t="s">
-        <v>45</v>
-      </c>
       <c r="Q8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="R8" t="s">
         <v>20</v>
@@ -2057,10 +2048,10 @@
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K9">
         <v>33106</v>
@@ -2072,22 +2063,22 @@
         <v>46189</v>
       </c>
       <c r="N9" t="s">
+        <v>46</v>
+      </c>
+      <c r="O9" t="s">
         <v>47</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>48</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
+        <v>116</v>
+      </c>
+      <c r="R9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S9" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>119</v>
-      </c>
-      <c r="R9" t="s">
-        <v>57</v>
-      </c>
-      <c r="S9" s="11" t="s">
-        <v>50</v>
       </c>
       <c r="T9" s="4">
         <v>27.02</v>
@@ -2148,10 +2139,10 @@
         <v>3</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -2163,19 +2154,19 @@
         <v>46190</v>
       </c>
       <c r="N10" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" t="s">
+        <v>47</v>
+      </c>
+      <c r="P10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" t="s">
         <v>51</v>
       </c>
-      <c r="O10" t="s">
-        <v>48</v>
-      </c>
-      <c r="P10" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>52</v>
-      </c>
-      <c r="R10" t="s">
-        <v>53</v>
       </c>
       <c r="S10" s="4">
         <v>27.22</v>
@@ -2198,7 +2189,7 @@
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" t="str">
         <f>IF(
@@ -2241,10 +2232,10 @@
         <v>2</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K11">
         <v>33129</v>
@@ -2256,19 +2247,19 @@
         <v>46192</v>
       </c>
       <c r="N11" t="s">
+        <v>53</v>
+      </c>
+      <c r="O11" t="s">
         <v>54</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>55</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
+        <v>58</v>
+      </c>
+      <c r="R11" t="s">
         <v>56</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>59</v>
-      </c>
-      <c r="R11" t="s">
-        <v>57</v>
       </c>
       <c r="S11" s="4">
         <v>25.08</v>
@@ -2332,10 +2323,10 @@
         <v>3</v>
       </c>
       <c r="I12" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K12">
         <v>199763</v>
@@ -2347,19 +2338,19 @@
         <v>46191</v>
       </c>
       <c r="N12" t="s">
+        <v>61</v>
+      </c>
+      <c r="O12" t="s">
         <v>62</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q12" t="s">
         <v>63</v>
       </c>
-      <c r="P12" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>64</v>
-      </c>
       <c r="R12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S12" s="4">
         <v>27.8</v>
@@ -2423,10 +2414,10 @@
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K13">
         <v>199764</v>
@@ -2434,23 +2425,23 @@
       <c r="L13" s="3">
         <v>46191</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="M13" s="3">
+        <v>46191</v>
+      </c>
+      <c r="N13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O13" t="s">
         <v>66</v>
       </c>
-      <c r="N13" t="s">
+      <c r="P13" t="s">
         <v>67</v>
       </c>
-      <c r="O13" t="s">
-        <v>68</v>
-      </c>
-      <c r="P13" t="s">
-        <v>69</v>
-      </c>
       <c r="Q13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S13" s="4">
         <v>25.4</v>
@@ -2514,10 +2505,10 @@
         <v>2</v>
       </c>
       <c r="I14" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K14">
         <v>199765</v>
@@ -2529,7 +2520,7 @@
         <v>46191</v>
       </c>
       <c r="N14" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="O14" t="s">
         <v>18</v>
@@ -2538,10 +2529,10 @@
         <v>19</v>
       </c>
       <c r="Q14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S14" s="4">
         <v>26.8</v>
@@ -2564,7 +2555,7 @@
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C15" t="str">
         <f>IF(
@@ -2609,13 +2600,13 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L15" s="3">
         <v>46192</v>
@@ -2624,19 +2615,19 @@
         <v>46192</v>
       </c>
       <c r="N15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q15" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="R15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S15" s="4">
         <v>26.4</v>
@@ -2700,10 +2691,10 @@
         <v>3</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K16">
         <v>199767</v>
@@ -2715,19 +2706,19 @@
         <v>46191</v>
       </c>
       <c r="N16" t="s">
+        <v>28</v>
+      </c>
+      <c r="O16" t="s">
         <v>29</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>30</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
+        <v>37</v>
+      </c>
+      <c r="R16" t="s">
         <v>31</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>38</v>
-      </c>
-      <c r="R16" t="s">
-        <v>32</v>
       </c>
       <c r="S16" s="4">
         <v>25.7</v>
@@ -2750,7 +2741,7 @@
     <row r="17" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C17" t="str">
         <f>IF(
@@ -2787,13 +2778,13 @@
         <v/>
       </c>
       <c r="I17" t="s">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="J17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L17" s="3">
         <v>46191</v>
@@ -2802,19 +2793,19 @@
         <v>46192</v>
       </c>
       <c r="N17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O17" t="s">
+        <v>77</v>
+      </c>
+      <c r="P17" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q17" t="s">
         <v>79</v>
       </c>
-      <c r="P17" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>82</v>
-      </c>
       <c r="R17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S17" s="4">
         <v>27.62</v>
@@ -2875,10 +2866,10 @@
         <v>2</v>
       </c>
       <c r="I18" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K18">
         <v>7</v>
@@ -2890,16 +2881,16 @@
         <v>46192</v>
       </c>
       <c r="N18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O18" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P18" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q18" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="R18" t="s">
         <v>20</v>
@@ -2966,10 +2957,10 @@
         <v>3</v>
       </c>
       <c r="I19" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K19">
         <v>25</v>
@@ -2981,19 +2972,19 @@
         <v>46192</v>
       </c>
       <c r="N19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="P19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="R19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S19" s="4">
         <v>27.18</v>
@@ -3057,10 +3048,10 @@
         <v>3</v>
       </c>
       <c r="I20" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K20">
         <v>293</v>
@@ -3072,19 +3063,19 @@
         <v>46192</v>
       </c>
       <c r="N20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O20" t="s">
+        <v>43</v>
+      </c>
+      <c r="P20" t="s">
         <v>44</v>
       </c>
-      <c r="P20" t="s">
-        <v>45</v>
-      </c>
       <c r="Q20" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="R20" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S20" s="4">
         <v>27.14</v>
@@ -3148,10 +3139,10 @@
         <v>5</v>
       </c>
       <c r="I21" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J21" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -3163,16 +3154,16 @@
         <v>46193</v>
       </c>
       <c r="N21" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O21" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="R21" t="s">
         <v>20</v>
@@ -3239,10 +3230,10 @@
         <v>2</v>
       </c>
       <c r="I22" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K22">
         <v>199781</v>
@@ -3254,19 +3245,19 @@
         <v>46192</v>
       </c>
       <c r="N22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O22" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S22" s="4">
         <v>27.88</v>
@@ -3330,31 +3321,31 @@
         <v>5</v>
       </c>
       <c r="I23" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J23" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K23">
         <v>2</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="M23" s="3">
         <v>46193</v>
       </c>
       <c r="N23" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="O23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P23" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="Q23" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="R23" t="s">
         <v>20</v>
@@ -3421,10 +3412,10 @@
         <v>2</v>
       </c>
       <c r="I24" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K24">
         <v>10</v>
@@ -3436,16 +3427,16 @@
         <v>46193</v>
       </c>
       <c r="N24" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q24" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="R24" t="s">
         <v>20</v>
@@ -3512,10 +3503,10 @@
         <v>4</v>
       </c>
       <c r="I25" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K25">
         <v>199783</v>
@@ -3527,19 +3518,19 @@
         <v>46193</v>
       </c>
       <c r="N25" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P25" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S25" s="4">
         <v>25.46</v>
@@ -3603,10 +3594,10 @@
         <v>4</v>
       </c>
       <c r="I26" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J26" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K26">
         <v>3</v>
@@ -3618,16 +3609,16 @@
         <v>46193</v>
       </c>
       <c r="N26" t="s">
+        <v>53</v>
+      </c>
+      <c r="O26" t="s">
         <v>54</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>55</v>
       </c>
-      <c r="P26" t="s">
-        <v>56</v>
-      </c>
       <c r="Q26" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="R26" t="s">
         <v>20</v>
@@ -3653,7 +3644,7 @@
     <row r="27" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C27" t="str">
         <f>IF(
@@ -3690,13 +3681,13 @@
         <v/>
       </c>
       <c r="I27" t="s">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="J27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K27" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L27" s="3">
         <v>46191</v>
@@ -3705,19 +3696,19 @@
         <v>46194</v>
       </c>
       <c r="N27" t="s">
+        <v>110</v>
+      </c>
+      <c r="O27" t="s">
+        <v>111</v>
+      </c>
+      <c r="P27" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q27" t="s">
         <v>113</v>
       </c>
-      <c r="O27" t="s">
-        <v>114</v>
-      </c>
-      <c r="P27" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>116</v>
-      </c>
       <c r="R27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S27" s="4">
         <v>26.56</v>
@@ -3778,10 +3769,10 @@
         <v>4</v>
       </c>
       <c r="I28" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K28">
         <v>199784</v>
@@ -3793,19 +3784,19 @@
         <v>46193</v>
       </c>
       <c r="N28" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O28" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S28" s="4">
         <v>25.42</v>
@@ -3869,10 +3860,10 @@
         <v>2</v>
       </c>
       <c r="I29" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K29">
         <v>199785</v>
@@ -3884,7 +3875,7 @@
         <v>46193</v>
       </c>
       <c r="N29" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="O29" t="s">
         <v>18</v>
@@ -3893,10 +3884,10 @@
         <v>19</v>
       </c>
       <c r="Q29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S29" s="4">
         <v>26.8</v>
@@ -3919,7 +3910,7 @@
     <row r="30" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C30" t="str">
         <f>IF(
@@ -3959,13 +3950,13 @@
         <v>2</v>
       </c>
       <c r="I30" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J30" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="L30" s="3">
         <v>46195</v>
@@ -3974,19 +3965,19 @@
         <v>46195</v>
       </c>
       <c r="N30" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O30" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P30" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q30" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="R30" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="S30" s="4">
         <v>23.8</v>
@@ -4006,7 +3997,7 @@
     <row r="31" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C31" t="str">
         <f>IF(
@@ -4046,13 +4037,13 @@
         <v>4</v>
       </c>
       <c r="I31" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J31" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L31" s="3">
         <v>46195</v>
@@ -4061,19 +4052,19 @@
         <v>46195</v>
       </c>
       <c r="N31" t="s">
+        <v>28</v>
+      </c>
+      <c r="O31" t="s">
         <v>29</v>
       </c>
-      <c r="O31" t="s">
+      <c r="P31" t="s">
         <v>30</v>
       </c>
-      <c r="P31" t="s">
-        <v>31</v>
-      </c>
       <c r="Q31" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="R31" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="S31" s="4">
         <v>23.8</v>
@@ -4093,7 +4084,7 @@
     <row r="32" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C32" t="str">
         <f>IF(
@@ -4133,13 +4124,13 @@
         <v>2</v>
       </c>
       <c r="I32" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J32" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L32" s="3">
         <v>46195</v>
@@ -4148,19 +4139,19 @@
         <v>46195</v>
       </c>
       <c r="N32" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="O32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q32" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="R32" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="S32" s="4">
         <v>24</v>
@@ -4180,7 +4171,7 @@
     <row r="33" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C33" t="str">
         <f>IF(
@@ -4220,13 +4211,13 @@
         <v>5</v>
       </c>
       <c r="I33" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J33" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="L33" s="3">
         <v>46195</v>
@@ -4235,19 +4226,19 @@
         <v>46195</v>
       </c>
       <c r="N33" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O33" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P33" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q33" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="R33" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="S33" s="4"/>
       <c r="V33" s="4" t="str">
@@ -4303,10 +4294,10 @@
         <v>3</v>
       </c>
       <c r="I34" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J34" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K34">
         <v>298</v>
@@ -4318,19 +4309,19 @@
         <v>46196</v>
       </c>
       <c r="N34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="O34" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="P34" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q34" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="R34" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S34" s="4">
         <v>26.2</v>
@@ -4393,13 +4384,13 @@
         <v>278</v>
       </c>
       <c r="I35" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J35" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K35" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L35" s="3">
         <v>46194</v>
@@ -4408,19 +4399,19 @@
         <v>46195</v>
       </c>
       <c r="N35" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O35" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P35" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q35" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="R35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S35" s="4">
         <v>28.68</v>
@@ -4483,13 +4474,13 @@
         <v>280</v>
       </c>
       <c r="I36" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J36" t="s">
+        <v>133</v>
+      </c>
+      <c r="K36" t="s">
         <v>136</v>
-      </c>
-      <c r="K36" t="s">
-        <v>139</v>
       </c>
       <c r="L36" s="3">
         <v>46195</v>
@@ -4498,19 +4489,19 @@
         <v>46196</v>
       </c>
       <c r="N36" t="s">
+        <v>46</v>
+      </c>
+      <c r="O36" t="s">
         <v>47</v>
       </c>
-      <c r="O36" t="s">
+      <c r="P36" t="s">
         <v>48</v>
       </c>
-      <c r="P36" t="s">
-        <v>49</v>
-      </c>
       <c r="Q36" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="R36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S36" s="4">
         <v>26.92</v>
@@ -4534,13 +4525,13 @@
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D37" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F37" s="4">
         <f>IF(Table1[[#This Row],[ціна за тонну з ПДВ]]/1.2=0, "", Table1[[#This Row],[ціна за тонну з ПДВ]]/1.2)</f>
@@ -4550,13 +4541,13 @@
         <v>7</v>
       </c>
       <c r="I37" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J37" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K37" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="L37" s="3">
         <v>46195</v>
@@ -4574,10 +4565,10 @@
         <v>19</v>
       </c>
       <c r="Q37" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="R37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S37" s="4">
         <v>26.9</v>
@@ -4641,10 +4632,10 @@
         <v>4</v>
       </c>
       <c r="I38" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K38">
         <v>4</v>
@@ -4656,16 +4647,16 @@
         <v>46193</v>
       </c>
       <c r="N38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O38" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q38" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="R38" t="s">
         <v>20</v>
@@ -4726,10 +4717,10 @@
         <v>833.33333333333337</v>
       </c>
       <c r="I39" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K39">
         <v>199842</v>
@@ -4741,19 +4732,19 @@
         <v>46197</v>
       </c>
       <c r="N39" t="s">
+        <v>142</v>
+      </c>
+      <c r="O39" t="s">
+        <v>143</v>
+      </c>
+      <c r="P39" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q39" t="s">
         <v>145</v>
       </c>
-      <c r="O39" t="s">
-        <v>146</v>
-      </c>
-      <c r="P39" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>148</v>
-      </c>
       <c r="R39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S39" s="4">
         <v>26.74</v>
@@ -4817,10 +4808,10 @@
         <v>5</v>
       </c>
       <c r="I40" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K40">
         <v>199838</v>
@@ -4832,19 +4823,19 @@
         <v>46196</v>
       </c>
       <c r="N40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O40" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P40" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>146</v>
+      </c>
+      <c r="R40" t="s">
         <v>31</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>149</v>
-      </c>
-      <c r="R40" t="s">
-        <v>32</v>
       </c>
       <c r="S40" s="4">
         <v>25.98</v>
@@ -4905,10 +4896,10 @@
         <v>282</v>
       </c>
       <c r="I41" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K41">
         <v>199841</v>
@@ -4920,19 +4911,19 @@
         <v>46197</v>
       </c>
       <c r="N41" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P41" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q41" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="R41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S41" s="4">
         <v>27.58</v>
@@ -4993,10 +4984,10 @@
         <v>282</v>
       </c>
       <c r="I42" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K42">
         <v>199835</v>
@@ -5008,19 +4999,19 @@
         <v>46196</v>
       </c>
       <c r="N42" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O42" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q42" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="R42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S42" s="4">
         <v>27.84</v>
@@ -5081,10 +5072,10 @@
         <v>282</v>
       </c>
       <c r="I43" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K43">
         <v>199837</v>
@@ -5096,19 +5087,19 @@
         <v>46197</v>
       </c>
       <c r="N43" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="O43" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q43" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="R43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S43" s="4">
         <v>25.48</v>
@@ -5169,10 +5160,10 @@
         <v>282</v>
       </c>
       <c r="I44" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K44">
         <v>199839</v>
@@ -5184,19 +5175,19 @@
         <v>46197</v>
       </c>
       <c r="N44" t="s">
+        <v>160</v>
+      </c>
+      <c r="O44" t="s">
+        <v>161</v>
+      </c>
+      <c r="P44" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q44" t="s">
         <v>163</v>
       </c>
-      <c r="O44" t="s">
-        <v>164</v>
-      </c>
-      <c r="P44" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>166</v>
-      </c>
       <c r="R44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S44" s="4">
         <v>27.08</v>
@@ -5257,10 +5248,10 @@
         <v>282</v>
       </c>
       <c r="I45" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K45">
         <v>199840</v>
@@ -5272,19 +5263,19 @@
         <v>46197</v>
       </c>
       <c r="N45" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O45" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P45" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q45" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="R45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S45" s="4">
         <v>26.96</v>
@@ -5345,10 +5336,10 @@
         <v>282</v>
       </c>
       <c r="I46" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K46">
         <v>199836</v>
@@ -5360,19 +5351,19 @@
         <v>46197</v>
       </c>
       <c r="N46" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q46" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="R46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S46" s="4">
         <v>28.1</v>
@@ -5433,10 +5424,10 @@
         <v>282</v>
       </c>
       <c r="I47" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K47">
         <v>199846</v>
@@ -5448,19 +5439,19 @@
         <v>46197</v>
       </c>
       <c r="N47" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O47" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P47" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="Q47" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="R47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S47" s="4">
         <v>25.34</v>
@@ -5521,10 +5512,10 @@
         <v>4</v>
       </c>
       <c r="I48" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K48">
         <v>199845</v>
@@ -5545,10 +5536,10 @@
         <v>19</v>
       </c>
       <c r="Q48" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="R48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S48" s="4">
         <v>26.82</v>
@@ -5612,10 +5603,10 @@
         <v>5</v>
       </c>
       <c r="I49" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J49" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K49">
         <v>259</v>
@@ -5627,19 +5618,19 @@
         <v>46197</v>
       </c>
       <c r="N49" t="s">
+        <v>46</v>
+      </c>
+      <c r="O49" t="s">
         <v>47</v>
       </c>
-      <c r="O49" t="s">
+      <c r="P49" t="s">
         <v>48</v>
       </c>
-      <c r="P49" t="s">
-        <v>49</v>
-      </c>
       <c r="Q49" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S49" s="4">
         <v>27.1</v>
@@ -5699,10 +5690,10 @@
         <v>2</v>
       </c>
       <c r="I50" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J50" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K50">
         <v>1</v>
@@ -5714,19 +5705,19 @@
         <v>46198</v>
       </c>
       <c r="N50" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O50" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P50" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q50" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="R50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S50" s="4">
         <v>27.72</v>
@@ -5787,10 +5778,10 @@
         <v>2</v>
       </c>
       <c r="I51" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J51" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K51">
         <v>2</v>
@@ -5802,19 +5793,19 @@
         <v>46198</v>
       </c>
       <c r="N51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O51" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P51" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Q51" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="R51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S51" s="4">
         <v>24.9</v>
@@ -5834,7 +5825,7 @@
     <row r="52" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C52" t="str">
         <f>IF(
@@ -5871,10 +5862,10 @@
         <v/>
       </c>
       <c r="I52" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J52" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K52">
         <v>1293</v>
@@ -5886,19 +5877,19 @@
         <v>46198</v>
       </c>
       <c r="N52" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O52" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P52" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q52" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="R52" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S52" s="4">
         <v>27.08</v>
@@ -5918,7 +5909,7 @@
     <row r="53" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C53" t="str">
         <f>IF(
@@ -5955,10 +5946,10 @@
         <v/>
       </c>
       <c r="I53" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J53" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K53">
         <v>1144</v>
@@ -5970,19 +5961,19 @@
         <v>46198</v>
       </c>
       <c r="N53" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="O53" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P53" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="Q53" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="R53" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S53" s="4">
         <v>27.32</v>
@@ -6002,7 +5993,7 @@
     <row r="54" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C54" t="str">
         <f>IF(
@@ -6039,10 +6030,10 @@
         <v/>
       </c>
       <c r="I54" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="J54" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K54">
         <v>320</v>
@@ -6054,19 +6045,19 @@
         <v>46198</v>
       </c>
       <c r="N54" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O54" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q54" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="R54" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="S54" s="4">
         <v>27.64</v>
@@ -6331,7 +6322,7 @@
     <row r="60" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A60" s="10"/>
       <c r="B60" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60"/>
@@ -6354,7 +6345,7 @@
     </row>
     <row r="69" spans="19:19" x14ac:dyDescent="0.45">
       <c r="S69" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
